--- a/docs/students/7b.xlsx
+++ b/docs/students/7b.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\María Alexandra\Listados Actualizados\LISTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\AgenteIA_Alexandra\docs\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F4D084-4A63-436A-A771-3C6EF9E05833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC7D99E-F78B-4878-939A-5BF7A21F2452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="100">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -353,13 +353,22 @@
   </si>
   <si>
     <t>23AC0191@cac.edu.co</t>
+  </si>
+  <si>
+    <t>NOMBRE  PAPÁ</t>
+  </si>
+  <si>
+    <t>ID_DRIVE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,11 +407,6 @@
       <color rgb="FF181818"/>
       <name val="Aptos Light"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Josefin Sans Light"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -418,7 +422,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -442,9 +446,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </left>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -460,12 +471,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -483,7 +491,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -825,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="36.375" customWidth="1"/>
@@ -834,342 +847,402 @@
     <col min="4" max="4" width="46.875" customWidth="1"/>
     <col min="5" max="5" width="41.875" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="77.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15">
-      <c r="A2" s="5" t="s">
+      <c r="G1" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15">
-      <c r="A3" s="6" t="s">
+      <c r="G2" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
-      <c r="A4" s="6" t="s">
+      <c r="G3" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="15">
-      <c r="A5" s="6" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" s="6" t="s">
+      <c r="G5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
-      <c r="A7" s="6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>86</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" s="6" t="s">
+      <c r="G7" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7" t="s">
+      <c r="G8" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" s="6" t="s">
+      <c r="G9" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>89</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" s="6" t="s">
+      <c r="G10" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
+      <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
-      <c r="A12" s="6" t="s">
+      <c r="G11" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
+      <c r="A12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
-      <c r="A13" s="6" t="s">
+      <c r="G12" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.25">
-      <c r="A14" s="6" t="s">
+      <c r="G13" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="A14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" spans="1:7" ht="15">
-      <c r="A15" s="6" t="s">
+      <c r="G14" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="A15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="15">
-      <c r="A16" s="6" t="s">
+      <c r="G15" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>73</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="6" t="s">
+      <c r="G16" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="G17" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="G19" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1219,10 +1292,13 @@
     <hyperlink ref="F17" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
     <hyperlink ref="D15" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
     <hyperlink ref="F15" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="G2" r:id="rId47" xr:uid="{47161B6E-2147-4F6B-9F4D-5F676EA67682}"/>
+    <hyperlink ref="G3:G13" r:id="rId48" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{89567BFF-CEA1-4124-94F1-15C4A2FC1490}"/>
+    <hyperlink ref="G14:G19" r:id="rId49" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{38482626-570A-4E38-9AED-0086EFD35196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId47"/>
-  <legacyDrawing r:id="rId48"/>
+  <pageSetup orientation="portrait" r:id="rId50"/>
+  <legacyDrawing r:id="rId51"/>
 </worksheet>
 </file>
 
